--- a/output/StructureDefinition-ConsentTemplate.xlsx
+++ b/output/StructureDefinition-ConsentTemplate.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6051" uniqueCount="795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6053" uniqueCount="794">
   <si>
     <t>Property</t>
   </si>
@@ -2034,10 +2034,6 @@
   </si>
   <si>
     <t>Questionnaire.item.text.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
   </si>
   <si>
     <t>Questionnaire.item.text.extension:renderingMarkdown.value[x]:valueMarkdown</t>
@@ -17363,14 +17359,16 @@
         <v>21</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="AC142" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD142" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AF142" t="s" s="2">
         <v>163</v>
@@ -17390,13 +17388,13 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>647</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D143" t="s" s="2">
         <v>21</v>
@@ -17492,13 +17490,13 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>633</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D144" t="s" s="2">
         <v>126</v>
@@ -17520,13 +17518,13 @@
         <v>21</v>
       </c>
       <c r="K144" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="L144" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="L144" t="s" s="2">
+      <c r="M144" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>130</v>
@@ -17596,7 +17594,7 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>640</v>
@@ -17696,7 +17694,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>642</v>
@@ -17798,7 +17796,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>644</v>
@@ -17841,7 +17839,7 @@
       </c>
       <c r="Q147" s="2"/>
       <c r="R147" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="S147" t="s" s="2">
         <v>21</v>
@@ -17900,7 +17898,7 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>647</v>
@@ -17971,14 +17969,16 @@
         <v>21</v>
       </c>
       <c r="AB148" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="AC148" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD148" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE148" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AF148" t="s" s="2">
         <v>163</v>
@@ -17998,13 +17998,13 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>647</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D149" t="s" s="2">
         <v>21</v>
@@ -18100,10 +18100,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18129,10 +18129,10 @@
         <v>143</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -18156,34 +18156,34 @@
         <v>21</v>
       </c>
       <c r="W150" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="X150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF150" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="X150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE150" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF150" t="s" s="2">
-        <v>666</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>75</v>
@@ -18200,10 +18200,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -18229,16 +18229,16 @@
         <v>103</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>668</v>
       </c>
-      <c r="M151" t="s" s="2">
+      <c r="N151" t="s" s="2">
         <v>669</v>
       </c>
-      <c r="N151" t="s" s="2">
+      <c r="O151" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>671</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>21</v>
@@ -18266,11 +18266,11 @@
         <v>175</v>
       </c>
       <c r="Y151" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="Z151" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="Z151" t="s" s="2">
-        <v>673</v>
-      </c>
       <c r="AA151" t="s" s="2">
         <v>21</v>
       </c>
@@ -18287,7 +18287,7 @@
         <v>21</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>82</v>
@@ -18304,10 +18304,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -18333,16 +18333,16 @@
         <v>544</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>675</v>
       </c>
-      <c r="M152" t="s" s="2">
+      <c r="N152" t="s" s="2">
         <v>676</v>
       </c>
-      <c r="N152" t="s" s="2">
+      <c r="O152" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="O152" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>21</v>
@@ -18391,7 +18391,7 @@
         <v>21</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>75</v>
@@ -18403,15 +18403,15 @@
         <v>94</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -18508,10 +18508,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -18610,13 +18610,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="C155" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="B155" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="C155" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="D155" t="s" s="2">
         <v>126</v>
@@ -18714,10 +18714,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="B156" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="B156" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18814,10 +18814,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="B157" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="B157" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18916,10 +18916,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="B158" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="B158" t="s" s="2">
-        <v>689</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -19018,10 +19018,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="B159" t="s" s="2">
         <v>690</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>691</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -19044,7 +19044,7 @@
         <v>21</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="L159" t="s" s="2">
         <v>161</v>
@@ -19118,10 +19118,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="B160" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -19218,10 +19218,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="B161" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>696</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -19320,10 +19320,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="B162" t="s" s="2">
         <v>697</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>698</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19422,10 +19422,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="B163" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="B163" t="s" s="2">
-        <v>700</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -19524,10 +19524,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="B164" t="s" s="2">
         <v>701</v>
-      </c>
-      <c r="B164" t="s" s="2">
-        <v>702</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -19626,10 +19626,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="B165" t="s" s="2">
         <v>703</v>
-      </c>
-      <c r="B165" t="s" s="2">
-        <v>704</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -19728,10 +19728,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -19832,10 +19832,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19861,13 +19861,13 @@
         <v>143</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="M167" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="M167" t="s" s="2">
+      <c r="N167" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -19917,7 +19917,7 @@
         <v>21</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>82</v>
@@ -19934,10 +19934,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19963,10 +19963,10 @@
         <v>103</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="M168" t="s" s="2">
         <v>711</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>712</v>
       </c>
       <c r="N168" t="s" s="2">
         <v>172</v>
@@ -19998,11 +19998,11 @@
         <v>175</v>
       </c>
       <c r="Y168" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="Z168" t="s" s="2">
         <v>713</v>
       </c>
-      <c r="Z168" t="s" s="2">
-        <v>714</v>
-      </c>
       <c r="AA168" t="s" s="2">
         <v>21</v>
       </c>
@@ -20019,7 +20019,7 @@
         <v>21</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>82</v>
@@ -20036,10 +20036,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -20062,13 +20062,13 @@
         <v>21</v>
       </c>
       <c r="K169" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="L169" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="L169" t="s" s="2">
+      <c r="M169" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>718</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -20098,37 +20098,37 @@
         <v>613</v>
       </c>
       <c r="Y169" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="Z169" t="s" s="2">
         <v>719</v>
       </c>
-      <c r="Z169" t="s" s="2">
+      <c r="AA169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF169" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="AG169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI169" t="s" s="2">
         <v>720</v>
-      </c>
-      <c r="AA169" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB169" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC169" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD169" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE169" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF169" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="AG169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH169" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI169" t="s" s="2">
-        <v>721</v>
       </c>
       <c r="AJ169" t="s" s="2">
         <v>95</v>
@@ -20136,10 +20136,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -20165,13 +20165,13 @@
         <v>103</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="M170" t="s" s="2">
         <v>723</v>
       </c>
-      <c r="M170" t="s" s="2">
+      <c r="N170" t="s" s="2">
         <v>724</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>725</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -20200,37 +20200,37 @@
         <v>175</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="Z170" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="AA170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF170" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="AG170" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI170" t="s" s="2">
         <v>726</v>
-      </c>
-      <c r="AA170" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB170" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC170" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD170" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE170" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF170" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="AG170" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI170" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="AJ170" t="s" s="2">
         <v>95</v>
@@ -20238,10 +20238,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -20267,74 +20267,74 @@
         <v>288</v>
       </c>
       <c r="L171" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="M171" t="s" s="2">
         <v>729</v>
       </c>
-      <c r="M171" t="s" s="2">
+      <c r="N171" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q171" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="R171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF171" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="AG171" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI171" t="s" s="2">
         <v>732</v>
-      </c>
-      <c r="R171" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S171" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T171" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U171" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V171" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W171" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X171" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y171" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z171" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA171" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB171" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC171" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD171" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE171" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF171" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="AG171" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH171" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI171" t="s" s="2">
-        <v>733</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>95</v>
@@ -20342,10 +20342,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -20371,23 +20371,23 @@
         <v>288</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>734</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>735</v>
       </c>
-      <c r="M172" t="s" s="2">
+      <c r="N172" t="s" s="2">
         <v>736</v>
       </c>
-      <c r="N172" t="s" s="2">
+      <c r="O172" t="s" s="2">
         <v>737</v>
       </c>
-      <c r="O172" t="s" s="2">
+      <c r="P172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q172" t="s" s="2">
         <v>738</v>
       </c>
-      <c r="P172" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q172" t="s" s="2">
-        <v>739</v>
-      </c>
       <c r="R172" t="s" s="2">
         <v>21</v>
       </c>
@@ -20431,7 +20431,7 @@
         <v>21</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>75</v>
@@ -20440,7 +20440,7 @@
         <v>82</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>95</v>
@@ -20448,10 +20448,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -20477,16 +20477,16 @@
         <v>288</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>741</v>
       </c>
-      <c r="M173" t="s" s="2">
+      <c r="N173" t="s" s="2">
         <v>742</v>
       </c>
-      <c r="N173" t="s" s="2">
+      <c r="O173" t="s" s="2">
         <v>743</v>
-      </c>
-      <c r="O173" t="s" s="2">
-        <v>744</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>21</v>
@@ -20535,7 +20535,7 @@
         <v>21</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>75</v>
@@ -20544,7 +20544,7 @@
         <v>82</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AJ173" t="s" s="2">
         <v>95</v>
@@ -20552,10 +20552,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -20578,16 +20578,16 @@
         <v>21</v>
       </c>
       <c r="K174" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="L174" t="s" s="2">
         <v>747</v>
       </c>
-      <c r="L174" t="s" s="2">
+      <c r="M174" t="s" s="2">
         <v>748</v>
       </c>
-      <c r="M174" t="s" s="2">
+      <c r="N174" t="s" s="2">
         <v>749</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>750</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -20637,7 +20637,7 @@
         <v>21</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>75</v>
@@ -20646,7 +20646,7 @@
         <v>82</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="AJ174" t="s" s="2">
         <v>95</v>
@@ -20654,10 +20654,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -20680,16 +20680,16 @@
         <v>21</v>
       </c>
       <c r="K175" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="L175" t="s" s="2">
         <v>753</v>
       </c>
-      <c r="L175" t="s" s="2">
+      <c r="M175" t="s" s="2">
         <v>754</v>
       </c>
-      <c r="M175" t="s" s="2">
+      <c r="N175" t="s" s="2">
         <v>755</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>756</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -20739,7 +20739,7 @@
         <v>21</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>75</v>
@@ -20748,7 +20748,7 @@
         <v>82</v>
       </c>
       <c r="AI175" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AJ175" t="s" s="2">
         <v>95</v>
@@ -20756,10 +20756,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -20785,13 +20785,13 @@
         <v>544</v>
       </c>
       <c r="L176" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="M176" t="s" s="2">
         <v>759</v>
       </c>
-      <c r="M176" t="s" s="2">
+      <c r="N176" t="s" s="2">
         <v>760</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>761</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -20841,7 +20841,7 @@
         <v>21</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>75</v>
@@ -20850,7 +20850,7 @@
         <v>76</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>95</v>
@@ -20858,10 +20858,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20958,10 +20958,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -21060,10 +21060,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -21164,10 +21164,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -21190,16 +21190,16 @@
         <v>21</v>
       </c>
       <c r="K180" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="L180" t="s" s="2">
         <v>766</v>
       </c>
-      <c r="L180" t="s" s="2">
+      <c r="M180" t="s" s="2">
         <v>767</v>
       </c>
-      <c r="M180" t="s" s="2">
+      <c r="N180" t="s" s="2">
         <v>768</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>769</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
@@ -21228,11 +21228,11 @@
         <v>613</v>
       </c>
       <c r="Y180" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="Z180" t="s" s="2">
         <v>719</v>
       </c>
-      <c r="Z180" t="s" s="2">
-        <v>720</v>
-      </c>
       <c r="AA180" t="s" s="2">
         <v>21</v>
       </c>
@@ -21249,7 +21249,7 @@
         <v>21</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>82</v>
@@ -21266,10 +21266,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -21295,20 +21295,20 @@
         <v>288</v>
       </c>
       <c r="L181" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="M181" t="s" s="2">
         <v>771</v>
       </c>
-      <c r="M181" t="s" s="2">
+      <c r="N181" t="s" s="2">
         <v>772</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>773</v>
       </c>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q181" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="R181" t="s" s="2">
         <v>21</v>
@@ -21353,7 +21353,7 @@
         <v>21</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>75</v>
@@ -21370,10 +21370,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -21399,16 +21399,16 @@
         <v>544</v>
       </c>
       <c r="L182" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="M182" t="s" s="2">
         <v>776</v>
       </c>
-      <c r="M182" t="s" s="2">
+      <c r="N182" t="s" s="2">
         <v>777</v>
       </c>
-      <c r="N182" t="s" s="2">
+      <c r="O182" t="s" s="2">
         <v>778</v>
-      </c>
-      <c r="O182" t="s" s="2">
-        <v>779</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>21</v>
@@ -21457,7 +21457,7 @@
         <v>21</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>75</v>
@@ -21466,7 +21466,7 @@
         <v>76</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>95</v>
@@ -21474,10 +21474,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -21574,10 +21574,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -21676,10 +21676,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -21780,10 +21780,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -21806,16 +21806,16 @@
         <v>21</v>
       </c>
       <c r="K186" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="L186" t="s" s="2">
         <v>785</v>
       </c>
-      <c r="L186" t="s" s="2">
+      <c r="M186" t="s" s="2">
         <v>786</v>
       </c>
-      <c r="M186" t="s" s="2">
+      <c r="N186" t="s" s="2">
         <v>787</v>
-      </c>
-      <c r="N186" t="s" s="2">
-        <v>788</v>
       </c>
       <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
@@ -21844,11 +21844,11 @@
         <v>613</v>
       </c>
       <c r="Y186" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="Z186" t="s" s="2">
         <v>719</v>
       </c>
-      <c r="Z186" t="s" s="2">
-        <v>720</v>
-      </c>
       <c r="AA186" t="s" s="2">
         <v>21</v>
       </c>
@@ -21865,7 +21865,7 @@
         <v>21</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>82</v>
@@ -21882,10 +21882,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -21911,16 +21911,16 @@
         <v>77</v>
       </c>
       <c r="L187" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="M187" t="s" s="2">
         <v>790</v>
       </c>
-      <c r="M187" t="s" s="2">
+      <c r="N187" t="s" s="2">
         <v>791</v>
       </c>
-      <c r="N187" t="s" s="2">
+      <c r="O187" t="s" s="2">
         <v>792</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>793</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>21</v>
@@ -21969,7 +21969,7 @@
         <v>21</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>75</v>
@@ -21978,7 +21978,7 @@
         <v>76</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>21</v>

--- a/output/StructureDefinition-ConsentTemplate.xlsx
+++ b/output/StructureDefinition-ConsentTemplate.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$177</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6053" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5737" uniqueCount="776">
   <si>
     <t>Property</t>
   </si>
@@ -2009,39 +2009,6 @@
     <t>This is an equivalent of the string on which the extension is sent, but includes additional markdown (see documentation about [markdown](http://hl7.org/fhir/R4/datatypes.html#markdown). Note that using HTML  [xhtml](http://hl7.org/fhir/R4/extension-rendering-xhtml.html) can allow for greater precision of display.</t>
   </si>
   <si>
-    <t>Questionnaire.item.text.extension:renderingMarkdown.id</t>
-  </si>
-  <si>
-    <t>Questionnaire.item.text.extension.id</t>
-  </si>
-  <si>
-    <t>Questionnaire.item.text.extension:renderingMarkdown.extension</t>
-  </si>
-  <si>
-    <t>Questionnaire.item.text.extension.extension</t>
-  </si>
-  <si>
-    <t>Questionnaire.item.text.extension:renderingMarkdown.url</t>
-  </si>
-  <si>
-    <t>Questionnaire.item.text.extension.url</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/rendering-markdown</t>
-  </si>
-  <si>
-    <t>Questionnaire.item.text.extension:renderingMarkdown.value[x]</t>
-  </si>
-  <si>
-    <t>Questionnaire.item.text.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Questionnaire.item.text.extension:renderingMarkdown.value[x]:valueMarkdown</t>
-  </si>
-  <si>
-    <t>valueMarkdown</t>
-  </si>
-  <si>
     <t>Questionnaire.item.text.extension:renderingXhtml</t>
   </si>
   <si>
@@ -2056,27 +2023,6 @@
   </si>
   <si>
     <t>This is an equivalent of the string on which the extension is sent, but includes additional XHTML markup, such as bold, italics, styles, tables, etc. Existing [restrictions on XHTML content](http://hl7.org/fhir/R4/narrative.html#security) apply. Note that using [markdown](http://hl7.org/fhir/R4/extension-rendering-markdown.html) allows for greater flexibility of display.</t>
-  </si>
-  <si>
-    <t>Questionnaire.item.text.extension:renderingXhtml.id</t>
-  </si>
-  <si>
-    <t>Questionnaire.item.text.extension:renderingXhtml.extension</t>
-  </si>
-  <si>
-    <t>Questionnaire.item.text.extension:renderingXhtml.url</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/rendering-xhtml</t>
-  </si>
-  <si>
-    <t>Questionnaire.item.text.extension:renderingXhtml.value[x]</t>
-  </si>
-  <si>
-    <t>Questionnaire.item.text.extension:renderingXhtml.value[x]:valueString</t>
-  </si>
-  <si>
-    <t>valueString</t>
   </si>
   <si>
     <t>Questionnaire.item.text.value</t>
@@ -2810,7 +2756,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ187"/>
+  <dimension ref="A1:AJ177"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="71.02734375" customWidth="true" bestFit="true"/>
@@ -16987,11 +16933,13 @@
         <v>639</v>
       </c>
       <c r="B139" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C139" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -17010,15 +16958,17 @@
         <v>21</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>143</v>
+        <v>641</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>144</v>
+        <v>642</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N139" s="2"/>
+        <v>643</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>21</v>
@@ -17067,38 +17017,38 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>21</v>
@@ -17110,17 +17060,15 @@
         <v>21</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>128</v>
+        <v>645</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>645</v>
+      </c>
+      <c r="N140" s="2"/>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>21</v>
@@ -17142,7 +17090,7 @@
         <v>21</v>
       </c>
       <c r="W140" t="s" s="2">
-        <v>21</v>
+        <v>646</v>
       </c>
       <c r="X140" t="s" s="2">
         <v>21</v>
@@ -17157,39 +17105,39 @@
         <v>21</v>
       </c>
       <c r="AB140" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="AC140" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="AD140" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE140" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>150</v>
+        <v>647</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="141" hidden="true">
+    <row r="141">
       <c r="A141" t="s" s="2">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17203,7 +17151,7 @@
         <v>82</v>
       </c>
       <c r="H141" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="I141" t="s" s="2">
         <v>21</v>
@@ -17212,24 +17160,26 @@
         <v>21</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>153</v>
+        <v>649</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>154</v>
+        <v>650</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="O141" s="2"/>
+        <v>651</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>652</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q141" s="2"/>
       <c r="R141" t="s" s="2">
-        <v>645</v>
+        <v>21</v>
       </c>
       <c r="S141" t="s" s="2">
         <v>21</v>
@@ -17247,13 +17197,13 @@
         <v>21</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>21</v>
+        <v>653</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>21</v>
+        <v>654</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>21</v>
@@ -17271,7 +17221,7 @@
         <v>21</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>157</v>
+        <v>648</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>82</v>
@@ -17280,18 +17230,18 @@
         <v>82</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>21</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="142" hidden="true">
+    <row r="142">
       <c r="A142" t="s" s="2">
-        <v>646</v>
+        <v>655</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -17299,31 +17249,35 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H142" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="I142" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J142" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>443</v>
+        <v>544</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>161</v>
+        <v>656</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N142" s="2"/>
-      <c r="O142" s="2"/>
+        <v>657</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>659</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>21</v>
       </c>
@@ -17371,37 +17325,35 @@
         <v>21</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>163</v>
+        <v>655</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>95</v>
+        <v>660</v>
       </c>
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>648</v>
+        <v>661</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="C143" t="s" s="2">
-        <v>649</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G143" t="s" s="2">
         <v>82</v>
@@ -17416,13 +17368,13 @@
         <v>21</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>443</v>
+        <v>143</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -17473,7 +17425,7 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>75</v>
@@ -17482,22 +17434,20 @@
         <v>82</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>95</v>
+        <v>21</v>
       </c>
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="C144" t="s" s="2">
-        <v>651</v>
-      </c>
+        <v>662</v>
+      </c>
+      <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
         <v>126</v>
       </c>
@@ -17506,7 +17456,7 @@
         <v>75</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>21</v>
@@ -17518,13 +17468,13 @@
         <v>21</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>652</v>
+        <v>127</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>653</v>
+        <v>128</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>654</v>
+        <v>149</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>130</v>
@@ -17565,16 +17515,16 @@
         <v>21</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="AC144" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="AD144" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE144" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="AF144" t="s" s="2">
         <v>150</v>
@@ -17592,16 +17542,18 @@
         <v>135</v>
       </c>
     </row>
-    <row r="145" hidden="true">
+    <row r="145">
       <c r="A145" t="s" s="2">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="C145" s="2"/>
+        <v>662</v>
+      </c>
+      <c r="C145" t="s" s="2">
+        <v>664</v>
+      </c>
       <c r="D145" t="s" s="2">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
@@ -17611,7 +17563,7 @@
         <v>82</v>
       </c>
       <c r="H145" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="I145" t="s" s="2">
         <v>21</v>
@@ -17620,15 +17572,17 @@
         <v>21</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>143</v>
+        <v>560</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N145" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>21</v>
@@ -17677,38 +17631,38 @@
         <v>21</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>642</v>
+        <v>666</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>21</v>
@@ -17720,17 +17674,15 @@
         <v>21</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="N146" s="2"/>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>21</v>
@@ -17767,50 +17719,50 @@
         <v>21</v>
       </c>
       <c r="AB146" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="AC146" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="AD146" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE146" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>135</v>
+        <v>21</v>
       </c>
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>657</v>
+        <v>667</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>644</v>
+        <v>668</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>21</v>
@@ -17822,16 +17774,16 @@
         <v>21</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -17839,7 +17791,7 @@
       </c>
       <c r="Q147" s="2"/>
       <c r="R147" t="s" s="2">
-        <v>658</v>
+        <v>21</v>
       </c>
       <c r="S147" t="s" s="2">
         <v>21</v>
@@ -17869,39 +17821,39 @@
         <v>21</v>
       </c>
       <c r="AB147" t="s" s="2">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="AC147" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="AD147" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE147" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>659</v>
+        <v>669</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>647</v>
+        <v>670</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17924,22 +17876,24 @@
         <v>21</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>143</v>
+        <v>97</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N148" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q148" s="2"/>
       <c r="R148" t="s" s="2">
-        <v>21</v>
+        <v>567</v>
       </c>
       <c r="S148" t="s" s="2">
         <v>21</v>
@@ -17981,31 +17935,29 @@
         <v>21</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>95</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="149" hidden="true">
+    <row r="149">
       <c r="A149" t="s" s="2">
-        <v>660</v>
+        <v>671</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="C149" t="s" s="2">
-        <v>661</v>
-      </c>
+        <v>672</v>
+      </c>
+      <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
         <v>21</v>
       </c>
@@ -18017,7 +17969,7 @@
         <v>82</v>
       </c>
       <c r="H149" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="I149" t="s" s="2">
         <v>21</v>
@@ -18026,7 +17978,7 @@
         <v>21</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>143</v>
+        <v>673</v>
       </c>
       <c r="L149" t="s" s="2">
         <v>161</v>
@@ -18100,10 +18052,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>662</v>
+        <v>674</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>662</v>
+        <v>675</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18129,10 +18081,10 @@
         <v>143</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>663</v>
+        <v>144</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>663</v>
+        <v>145</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -18156,7 +18108,7 @@
         <v>21</v>
       </c>
       <c r="W150" t="s" s="2">
-        <v>664</v>
+        <v>21</v>
       </c>
       <c r="X150" t="s" s="2">
         <v>21</v>
@@ -18183,7 +18135,7 @@
         <v>21</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>665</v>
+        <v>146</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>75</v>
@@ -18198,26 +18150,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>666</v>
+        <v>677</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="I151" t="s" s="2">
         <v>21</v>
@@ -18226,20 +18178,18 @@
         <v>21</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>667</v>
+        <v>128</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>668</v>
+        <v>149</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>670</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>21</v>
       </c>
@@ -18263,51 +18213,51 @@
         <v>21</v>
       </c>
       <c r="X151" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>671</v>
+        <v>21</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>672</v>
+        <v>21</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="AC151" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="AD151" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE151" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>666</v>
+        <v>150</v>
       </c>
       <c r="AG151" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>95</v>
+        <v>135</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -18315,35 +18265,33 @@
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J152" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="J152" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K152" t="s" s="2">
-        <v>544</v>
+        <v>143</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>674</v>
+        <v>477</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>675</v>
+        <v>478</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="O152" t="s" s="2">
-        <v>677</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
         <v>21</v>
       </c>
@@ -18391,27 +18339,27 @@
         <v>21</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>673</v>
+        <v>480</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>94</v>
+        <v>481</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>678</v>
+        <v>95</v>
       </c>
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -18422,7 +18370,7 @@
         <v>75</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>21</v>
@@ -18431,18 +18379,20 @@
         <v>21</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>143</v>
+        <v>97</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>144</v>
+        <v>483</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N153" s="2"/>
+        <v>484</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>21</v>
@@ -18467,13 +18417,13 @@
         <v>21</v>
       </c>
       <c r="X153" t="s" s="2">
-        <v>21</v>
+        <v>244</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>21</v>
+        <v>486</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>21</v>
+        <v>487</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>21</v>
@@ -18491,7 +18441,7 @@
         <v>21</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>146</v>
+        <v>488</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>75</v>
@@ -18500,29 +18450,29 @@
         <v>82</v>
       </c>
       <c r="AI153" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>21</v>
+        <v>95</v>
       </c>
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>21</v>
@@ -18531,19 +18481,19 @@
         <v>21</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>127</v>
+        <v>341</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>128</v>
+        <v>490</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>149</v>
+        <v>491</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>130</v>
+        <v>492</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -18581,73 +18531,71 @@
         <v>21</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>150</v>
+        <v>493</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI154" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>135</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="C155" t="s" s="2">
-        <v>682</v>
-      </c>
+        <v>685</v>
+      </c>
+      <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J155" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="I155" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J155" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K155" t="s" s="2">
-        <v>560</v>
+        <v>143</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>139</v>
+        <v>495</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>140</v>
+        <v>496</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>130</v>
+        <v>497</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -18697,59 +18645,63 @@
         <v>21</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>150</v>
+        <v>498</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>135</v>
+        <v>95</v>
       </c>
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>21</v>
+        <v>594</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I156" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>144</v>
+        <v>595</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N156" s="2"/>
-      <c r="O156" s="2"/>
+        <v>596</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="O156" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="P156" t="s" s="2">
         <v>21</v>
       </c>
@@ -18797,41 +18749,41 @@
         <v>21</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>146</v>
+        <v>597</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
     </row>
-    <row r="157" hidden="true">
+    <row r="157">
       <c r="A157" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>21</v>
@@ -18840,16 +18792,16 @@
         <v>21</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>128</v>
+        <v>688</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>149</v>
+        <v>689</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>130</v>
+        <v>690</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -18887,39 +18839,39 @@
         <v>21</v>
       </c>
       <c r="AB157" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="AC157" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="AD157" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE157" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>150</v>
+        <v>687</v>
       </c>
       <c r="AG157" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>135</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="158" hidden="true">
+    <row r="158">
       <c r="A158" t="s" s="2">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -18933,7 +18885,7 @@
         <v>82</v>
       </c>
       <c r="H158" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="I158" t="s" s="2">
         <v>21</v>
@@ -18942,16 +18894,16 @@
         <v>21</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>153</v>
+        <v>692</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>154</v>
+        <v>693</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -18959,7 +18911,7 @@
       </c>
       <c r="Q158" s="2"/>
       <c r="R158" t="s" s="2">
-        <v>567</v>
+        <v>21</v>
       </c>
       <c r="S158" t="s" s="2">
         <v>21</v>
@@ -18977,13 +18929,13 @@
         <v>21</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>21</v>
+        <v>694</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>21</v>
+        <v>695</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>21</v>
@@ -19001,7 +18953,7 @@
         <v>21</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>157</v>
+        <v>691</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>82</v>
@@ -19010,18 +18962,18 @@
         <v>82</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>21</v>
+        <v>95</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -19044,13 +18996,13 @@
         <v>21</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>161</v>
+        <v>698</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>162</v>
+        <v>699</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -19077,13 +19029,13 @@
         <v>21</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>21</v>
+        <v>613</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>21</v>
+        <v>700</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>21</v>
+        <v>701</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>21</v>
@@ -19101,16 +19053,16 @@
         <v>21</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>163</v>
+        <v>696</v>
       </c>
       <c r="AG159" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH159" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI159" t="s" s="2">
-        <v>94</v>
+        <v>702</v>
       </c>
       <c r="AJ159" t="s" s="2">
         <v>95</v>
@@ -19118,10 +19070,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>692</v>
+        <v>703</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>693</v>
+        <v>703</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -19144,15 +19096,17 @@
         <v>21</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>144</v>
+        <v>704</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N160" s="2"/>
+        <v>705</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>706</v>
+      </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>21</v>
@@ -19177,13 +19131,13 @@
         <v>21</v>
       </c>
       <c r="X160" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>21</v>
+        <v>705</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>21</v>
+        <v>707</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>21</v>
@@ -19201,7 +19155,7 @@
         <v>21</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>146</v>
+        <v>703</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>75</v>
@@ -19210,32 +19164,32 @@
         <v>82</v>
       </c>
       <c r="AI160" t="s" s="2">
-        <v>21</v>
+        <v>708</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>21</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="161" hidden="true">
+    <row r="161">
       <c r="A161" t="s" s="2">
-        <v>694</v>
+        <v>709</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>695</v>
+        <v>709</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H161" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="I161" t="s" s="2">
         <v>21</v>
@@ -19244,22 +19198,24 @@
         <v>21</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>127</v>
+        <v>288</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>128</v>
+        <v>710</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>149</v>
+        <v>711</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>130</v>
+        <v>712</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q161" s="2"/>
+      <c r="Q161" t="s" s="2">
+        <v>713</v>
+      </c>
       <c r="R161" t="s" s="2">
         <v>21</v>
       </c>
@@ -19291,39 +19247,39 @@
         <v>21</v>
       </c>
       <c r="AB161" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="AC161" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="AD161" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE161" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>150</v>
+        <v>709</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>94</v>
+        <v>714</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>135</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>696</v>
+        <v>715</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>697</v>
+        <v>715</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19331,37 +19287,41 @@
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G162" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H162" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="I162" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>143</v>
+        <v>288</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>477</v>
+        <v>716</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>478</v>
+        <v>717</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="O162" s="2"/>
+        <v>718</v>
+      </c>
+      <c r="O162" t="s" s="2">
+        <v>719</v>
+      </c>
       <c r="P162" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q162" s="2"/>
+      <c r="Q162" t="s" s="2">
+        <v>720</v>
+      </c>
       <c r="R162" t="s" s="2">
         <v>21</v>
       </c>
@@ -19405,7 +19365,7 @@
         <v>21</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>480</v>
+        <v>715</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>75</v>
@@ -19414,7 +19374,7 @@
         <v>82</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>481</v>
+        <v>714</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>95</v>
@@ -19422,10 +19382,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>698</v>
+        <v>721</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>699</v>
+        <v>721</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -19436,7 +19396,7 @@
         <v>75</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>21</v>
@@ -19445,21 +19405,23 @@
         <v>21</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>97</v>
+        <v>288</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>483</v>
+        <v>722</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>484</v>
+        <v>723</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="O163" s="2"/>
+        <v>724</v>
+      </c>
+      <c r="O163" t="s" s="2">
+        <v>725</v>
+      </c>
       <c r="P163" t="s" s="2">
         <v>21</v>
       </c>
@@ -19483,13 +19445,13 @@
         <v>21</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>244</v>
+        <v>21</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>486</v>
+        <v>21</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>487</v>
+        <v>21</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>21</v>
@@ -19507,7 +19469,7 @@
         <v>21</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>488</v>
+        <v>721</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>75</v>
@@ -19516,7 +19478,7 @@
         <v>82</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>94</v>
+        <v>726</v>
       </c>
       <c r="AJ163" t="s" s="2">
         <v>95</v>
@@ -19524,10 +19486,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>700</v>
+        <v>727</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>701</v>
+        <v>727</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -19538,7 +19500,7 @@
         <v>75</v>
       </c>
       <c r="G164" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H164" t="s" s="2">
         <v>21</v>
@@ -19547,19 +19509,19 @@
         <v>21</v>
       </c>
       <c r="J164" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>341</v>
+        <v>728</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>490</v>
+        <v>729</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>491</v>
+        <v>730</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>492</v>
+        <v>731</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -19609,7 +19571,7 @@
         <v>21</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>493</v>
+        <v>727</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>75</v>
@@ -19618,18 +19580,18 @@
         <v>82</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>94</v>
+        <v>732</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>95</v>
       </c>
     </row>
-    <row r="165" hidden="true">
+    <row r="165">
       <c r="A165" t="s" s="2">
-        <v>702</v>
+        <v>733</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>703</v>
+        <v>733</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -19640,28 +19602,28 @@
         <v>75</v>
       </c>
       <c r="G165" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J165" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>143</v>
+        <v>734</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>495</v>
+        <v>735</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>496</v>
+        <v>736</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>497</v>
+        <v>737</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -19711,7 +19673,7 @@
         <v>21</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>498</v>
+        <v>733</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>75</v>
@@ -19720,22 +19682,22 @@
         <v>82</v>
       </c>
       <c r="AI165" t="s" s="2">
-        <v>94</v>
+        <v>738</v>
       </c>
       <c r="AJ165" t="s" s="2">
         <v>95</v>
       </c>
     </row>
-    <row r="166" hidden="true">
+    <row r="166">
       <c r="A166" t="s" s="2">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>704</v>
+        <v>739</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
-        <v>594</v>
+        <v>21</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
@@ -19745,29 +19707,27 @@
         <v>76</v>
       </c>
       <c r="H166" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="I166" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="J166" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>127</v>
+        <v>544</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>595</v>
+        <v>740</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>596</v>
+        <v>741</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>742</v>
+      </c>
+      <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
         <v>21</v>
       </c>
@@ -19815,7 +19775,7 @@
         <v>21</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>597</v>
+        <v>739</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>75</v>
@@ -19824,18 +19784,18 @@
         <v>76</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>94</v>
+        <v>738</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>135</v>
+        <v>95</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>705</v>
+        <v>743</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>705</v>
+        <v>743</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19843,13 +19803,13 @@
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H167" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="I167" t="s" s="2">
         <v>21</v>
@@ -19861,14 +19821,12 @@
         <v>143</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>706</v>
+        <v>144</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>708</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="N167" s="2"/>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>21</v>
@@ -19917,41 +19875,41 @@
         <v>21</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>705</v>
+        <v>146</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>95</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>709</v>
+        <v>744</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H168" t="s" s="2">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="I168" t="s" s="2">
         <v>21</v>
@@ -19960,16 +19918,16 @@
         <v>21</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>710</v>
+        <v>128</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>711</v>
+        <v>149</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>172</v>
+        <v>130</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -19995,83 +19953,87 @@
         <v>21</v>
       </c>
       <c r="X168" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>712</v>
+        <v>21</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>713</v>
+        <v>21</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB168" t="s" s="2">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="AC168" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="AD168" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE168" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>709</v>
+        <v>150</v>
       </c>
       <c r="AG168" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI168" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>95</v>
+        <v>135</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>714</v>
+        <v>745</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>714</v>
+        <v>745</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>21</v>
+        <v>594</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I169" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="I169" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J169" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>715</v>
+        <v>127</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>716</v>
+        <v>595</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="N169" s="2"/>
-      <c r="O169" s="2"/>
+        <v>596</v>
+      </c>
+      <c r="N169" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="O169" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="P169" t="s" s="2">
         <v>21</v>
       </c>
@@ -20095,13 +20057,13 @@
         <v>21</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>613</v>
+        <v>21</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>718</v>
+        <v>21</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>719</v>
+        <v>21</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>21</v>
@@ -20119,27 +20081,27 @@
         <v>21</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>714</v>
+        <v>597</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI169" t="s" s="2">
-        <v>720</v>
+        <v>94</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>95</v>
+        <v>135</v>
       </c>
     </row>
-    <row r="170" hidden="true">
+    <row r="170">
       <c r="A170" t="s" s="2">
-        <v>721</v>
+        <v>746</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>721</v>
+        <v>746</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -20147,13 +20109,13 @@
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G170" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H170" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="I170" t="s" s="2">
         <v>21</v>
@@ -20162,16 +20124,16 @@
         <v>21</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>103</v>
+        <v>747</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>722</v>
+        <v>748</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>723</v>
+        <v>749</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>724</v>
+        <v>750</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -20197,13 +20159,13 @@
         <v>21</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>175</v>
+        <v>613</v>
       </c>
       <c r="Y170" t="s" s="2">
-        <v>723</v>
+        <v>700</v>
       </c>
       <c r="Z170" t="s" s="2">
-        <v>725</v>
+        <v>701</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>21</v>
@@ -20221,16 +20183,16 @@
         <v>21</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>721</v>
+        <v>746</v>
       </c>
       <c r="AG170" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH170" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>726</v>
+        <v>94</v>
       </c>
       <c r="AJ170" t="s" s="2">
         <v>95</v>
@@ -20238,10 +20200,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>727</v>
+        <v>751</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>727</v>
+        <v>751</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -20267,20 +20229,20 @@
         <v>288</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>728</v>
+        <v>752</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>729</v>
+        <v>753</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>730</v>
+        <v>754</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q171" t="s" s="2">
-        <v>731</v>
+        <v>755</v>
       </c>
       <c r="R171" t="s" s="2">
         <v>21</v>
@@ -20325,7 +20287,7 @@
         <v>21</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>727</v>
+        <v>751</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>75</v>
@@ -20334,18 +20296,18 @@
         <v>82</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>732</v>
+        <v>94</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>95</v>
       </c>
     </row>
-    <row r="172" hidden="true">
+    <row r="172">
       <c r="A172" t="s" s="2">
-        <v>733</v>
+        <v>756</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>733</v>
+        <v>756</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -20356,10 +20318,10 @@
         <v>75</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H172" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="I172" t="s" s="2">
         <v>21</v>
@@ -20368,26 +20330,24 @@
         <v>21</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>288</v>
+        <v>544</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>734</v>
+        <v>757</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>735</v>
+        <v>758</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>736</v>
+        <v>759</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>737</v>
+        <v>760</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q172" t="s" s="2">
-        <v>738</v>
-      </c>
+      <c r="Q172" s="2"/>
       <c r="R172" t="s" s="2">
         <v>21</v>
       </c>
@@ -20431,16 +20391,16 @@
         <v>21</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>733</v>
+        <v>756</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH172" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>732</v>
+        <v>761</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>95</v>
@@ -20448,10 +20408,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>739</v>
+        <v>762</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>739</v>
+        <v>762</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -20474,20 +20434,16 @@
         <v>21</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>288</v>
+        <v>143</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>740</v>
+        <v>144</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="N173" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="O173" t="s" s="2">
-        <v>743</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="N173" s="2"/>
+      <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
         <v>21</v>
       </c>
@@ -20535,7 +20491,7 @@
         <v>21</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>739</v>
+        <v>146</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>75</v>
@@ -20544,29 +20500,29 @@
         <v>82</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>744</v>
+        <v>21</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>95</v>
+        <v>21</v>
       </c>
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>745</v>
+        <v>763</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>745</v>
+        <v>763</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>21</v>
@@ -20578,16 +20534,16 @@
         <v>21</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>746</v>
+        <v>127</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>747</v>
+        <v>128</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>748</v>
+        <v>149</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>749</v>
+        <v>130</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -20625,73 +20581,75 @@
         <v>21</v>
       </c>
       <c r="AB174" t="s" s="2">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="AC174" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="AD174" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE174" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>745</v>
+        <v>150</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH174" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>750</v>
+        <v>94</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>95</v>
+        <v>135</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>751</v>
+        <v>764</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>751</v>
+        <v>764</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>21</v>
+        <v>594</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I175" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="I175" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J175" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>752</v>
+        <v>127</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>753</v>
+        <v>595</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>754</v>
+        <v>596</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="O175" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="O175" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="P175" t="s" s="2">
         <v>21</v>
       </c>
@@ -20739,27 +20697,27 @@
         <v>21</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>751</v>
+        <v>597</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH175" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI175" t="s" s="2">
-        <v>756</v>
+        <v>94</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>95</v>
+        <v>135</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -20767,10 +20725,10 @@
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>83</v>
@@ -20782,16 +20740,16 @@
         <v>21</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>544</v>
+        <v>766</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>759</v>
+        <v>768</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -20817,13 +20775,13 @@
         <v>21</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>21</v>
+        <v>613</v>
       </c>
       <c r="Y176" t="s" s="2">
-        <v>21</v>
+        <v>700</v>
       </c>
       <c r="Z176" t="s" s="2">
-        <v>21</v>
+        <v>701</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>21</v>
@@ -20841,27 +20799,27 @@
         <v>21</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="AG176" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>756</v>
+        <v>94</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>95</v>
       </c>
     </row>
-    <row r="177" hidden="true">
+    <row r="177">
       <c r="A177" t="s" s="2">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20872,10 +20830,10 @@
         <v>75</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H177" t="s" s="2">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="I177" t="s" s="2">
         <v>21</v>
@@ -20884,16 +20842,20 @@
         <v>21</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>144</v>
+        <v>771</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N177" s="2"/>
-      <c r="O177" s="2"/>
+        <v>772</v>
+      </c>
+      <c r="N177" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="O177" t="s" s="2">
+        <v>774</v>
+      </c>
       <c r="P177" t="s" s="2">
         <v>21</v>
       </c>
@@ -20941,1051 +20903,23 @@
         <v>21</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>146</v>
+        <v>770</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>21</v>
+        <v>775</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="178" hidden="true">
-      <c r="A178" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="B178" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="C178" s="2"/>
-      <c r="D178" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="E178" s="2"/>
-      <c r="F178" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G178" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H178" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I178" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J178" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K178" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="L178" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="M178" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="O178" s="2"/>
-      <c r="P178" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q178" s="2"/>
-      <c r="R178" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S178" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T178" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U178" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V178" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W178" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X178" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y178" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z178" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA178" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB178" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AC178" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AD178" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE178" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AF178" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AG178" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH178" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI178" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AJ178" t="s" s="2">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="179" hidden="true">
-      <c r="A179" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="C179" s="2"/>
-      <c r="D179" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="E179" s="2"/>
-      <c r="F179" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G179" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I179" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J179" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K179" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="L179" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="P179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q179" s="2"/>
-      <c r="R179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE179" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF179" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="AG179" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH179" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI179" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AJ179" t="s" s="2">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="C180" s="2"/>
-      <c r="D180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E180" s="2"/>
-      <c r="F180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H180" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K180" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="L180" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="M180" t="s" s="2">
-        <v>767</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>768</v>
-      </c>
-      <c r="O180" s="2"/>
-      <c r="P180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q180" s="2"/>
-      <c r="R180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X180" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="Y180" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="Z180" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="AA180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE180" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF180" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="AG180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH180" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI180" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AJ180" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s" s="2">
-        <v>769</v>
-      </c>
-      <c r="B181" t="s" s="2">
-        <v>769</v>
-      </c>
-      <c r="C181" s="2"/>
-      <c r="D181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E181" s="2"/>
-      <c r="F181" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H181" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K181" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="L181" t="s" s="2">
-        <v>770</v>
-      </c>
-      <c r="M181" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="O181" s="2"/>
-      <c r="P181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q181" t="s" s="2">
-        <v>773</v>
-      </c>
-      <c r="R181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE181" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF181" t="s" s="2">
-        <v>769</v>
-      </c>
-      <c r="AG181" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH181" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI181" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AJ181" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="B182" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="C182" s="2"/>
-      <c r="D182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E182" s="2"/>
-      <c r="F182" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G182" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H182" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K182" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="L182" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="M182" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="O182" t="s" s="2">
-        <v>778</v>
-      </c>
-      <c r="P182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q182" s="2"/>
-      <c r="R182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE182" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF182" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="AG182" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH182" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI182" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="AJ182" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="183" hidden="true">
-      <c r="A183" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="B183" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="C183" s="2"/>
-      <c r="D183" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E183" s="2"/>
-      <c r="F183" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H183" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I183" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J183" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K183" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="L183" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="M183" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N183" s="2"/>
-      <c r="O183" s="2"/>
-      <c r="P183" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q183" s="2"/>
-      <c r="R183" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S183" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T183" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U183" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V183" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W183" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X183" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y183" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z183" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA183" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB183" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC183" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD183" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE183" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF183" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AG183" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH183" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI183" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ183" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="184" hidden="true">
-      <c r="A184" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="B184" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="C184" s="2"/>
-      <c r="D184" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="E184" s="2"/>
-      <c r="F184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G184" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H184" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I184" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J184" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K184" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="L184" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="M184" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N184" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="O184" s="2"/>
-      <c r="P184" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q184" s="2"/>
-      <c r="R184" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S184" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T184" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U184" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V184" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W184" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X184" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y184" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z184" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA184" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB184" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AC184" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AD184" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE184" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AF184" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AG184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH184" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI184" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AJ184" t="s" s="2">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="185" hidden="true">
-      <c r="A185" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="B185" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="C185" s="2"/>
-      <c r="D185" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="E185" s="2"/>
-      <c r="F185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G185" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H185" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J185" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K185" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="L185" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="M185" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="O185" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="P185" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q185" s="2"/>
-      <c r="R185" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S185" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T185" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U185" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V185" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W185" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X185" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y185" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z185" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA185" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB185" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC185" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD185" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE185" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF185" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="AG185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH185" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI185" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AJ185" t="s" s="2">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="B186" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="C186" s="2"/>
-      <c r="D186" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E186" s="2"/>
-      <c r="F186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H186" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I186" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J186" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K186" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="L186" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="M186" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="N186" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="O186" s="2"/>
-      <c r="P186" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q186" s="2"/>
-      <c r="R186" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S186" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T186" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U186" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V186" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W186" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X186" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="Y186" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="Z186" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="AA186" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB186" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC186" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD186" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE186" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF186" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="AG186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH186" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI186" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AJ186" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s" s="2">
-        <v>788</v>
-      </c>
-      <c r="B187" t="s" s="2">
-        <v>788</v>
-      </c>
-      <c r="C187" s="2"/>
-      <c r="D187" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E187" s="2"/>
-      <c r="F187" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G187" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H187" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I187" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J187" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K187" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="L187" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="M187" t="s" s="2">
-        <v>790</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>792</v>
-      </c>
-      <c r="P187" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q187" s="2"/>
-      <c r="R187" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S187" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T187" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U187" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V187" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W187" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X187" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y187" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z187" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA187" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB187" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC187" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD187" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE187" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF187" t="s" s="2">
-        <v>788</v>
-      </c>
-      <c r="AG187" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH187" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI187" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="AJ187" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ187">
+  <autoFilter ref="A1:AJ177">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -21995,7 +20929,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI186">
+  <conditionalFormatting sqref="A2:AI176">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
